--- a/artfynd/A 63930-2023 artfynd.xlsx
+++ b/artfynd/A 63930-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 63930-2023 artfynd.xlsx
+++ b/artfynd/A 63930-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>113165654</v>
       </c>
       <c r="B2" t="n">
-        <v>86137</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87412</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,14 +695,10 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Schaeff. : Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>1</t>
@@ -794,12 +785,7 @@
         <v>113165655</v>
       </c>
       <c r="B3" t="n">
-        <v>91263</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,7 +807,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -904,6 +890,319 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>113165656</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91443</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5754</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gultoppig fingersvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Ramaria testaceoflava</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Skutetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>482773</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6985316</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Äldre högörtsgranskog i skärning mot bäckmiljö</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>112882215</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skutetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>482855</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6985293</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Thomas Stålhandske</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Thomas Stålhandske</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>112882216</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skutetjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>482845</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6985295</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Thomas Stålhandske</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Thomas Stålhandske</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63930-2023 artfynd.xlsx
+++ b/artfynd/A 63930-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165654</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165655</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113165656</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1102,6 +1122,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882215</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1203,8 +1228,20 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112882216</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>